--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4804-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4804-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53950DD0-95F5-443E-8D97-2D8A8A589FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9E95734-EDB1-44C2-9878-A74795122E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{53B61911-D90B-426E-9744-4A3ECEF92884}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{69A32E2C-60D3-4B56-80E1-C2E9920F1F0F}"/>
   </bookViews>
   <sheets>
     <sheet name="4804-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1448,23 +1448,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD64FE98-51F8-4CCF-8021-E26AA1405933}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5144D1E-A178-4440-9A56-09448FF4C7AD}">
   <dimension ref="A1:R24"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.5546875" customWidth="1"/>
+    <col min="1" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10.625" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.625" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1492,7 +1492,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1522,7 +1522,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1618,7 +1618,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2024</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2023</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2020</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2019</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2018</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>2017</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2016</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2015</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
         <v>35</v>
       </c>
